--- a/results/reliability_eval/Llama-3-8B_P101_sample_15_tokens_0.1_temp_direct_query_scores_08-24-4.xlsx
+++ b/results/reliability_eval/Llama-3-8B_P101_sample_15_tokens_0.1_temp_direct_query_scores_08-24-4.xlsx
@@ -477,31 +477,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.5037788331071913</v>
+        <v>0.594208</v>
       </c>
       <c r="B2" t="n">
-        <v>0.3362739839583877</v>
+        <v>0.1549356358990444</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5037788331071913</v>
+        <v>0.594208</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3362739839583877</v>
+        <v>0.1549356358990444</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5029149706015378</v>
+        <v>0.4103725714285715</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3469024472300921</v>
+        <v>0.1089535576298613</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9956580732700135</v>
+        <v>0.9942171428571429</v>
       </c>
       <c r="H2" t="n">
-        <v>0.98927875874372</v>
+        <v>0.9545241054507927</v>
       </c>
       <c r="I2" t="n">
-        <v>0.33</v>
+        <v>0.125</v>
       </c>
     </row>
   </sheetData>
